--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
@@ -49,33 +49,27 @@
     <t xml:space="preserve">metric_label</t>
   </si>
   <si>
+    <t xml:space="preserve">Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porvenir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">austral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macrozona Austral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor (%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aysen</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">austral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macrozona Austral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magallanes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porvenir</t>
-  </si>
-  <si>
     <t xml:space="preserve">11102</t>
   </si>
   <si>
@@ -100,12 +94,6 @@
     <t xml:space="preserve">Chile Chico</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11402</t>
   </si>
   <si>
@@ -937,6 +925,12 @@
     <t xml:space="preserve">Zapallar</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">7305</t>
   </si>
   <si>
@@ -1321,6 +1315,12 @@
     <t xml:space="preserve">Pozo Almonte</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">4201</t>
   </si>
   <si>
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:27</t>
+    <t xml:space="preserve">2026-09-09 20:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2593,7 +2593,7 @@
         <v>2019</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
@@ -2614,7 +2614,7 @@
         <v>15</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7</v>
+        <v>6.29</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>15</v>
@@ -2625,7 +2625,7 @@
         <v>2019</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -2646,7 +2646,7 @@
         <v>15</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6.29</v>
+        <v>6</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>15</v>
@@ -2660,7 +2660,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>19</v>
@@ -2678,7 +2678,7 @@
         <v>15</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>15</v>
@@ -2692,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>21</v>
@@ -2710,7 +2710,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5.94</v>
+        <v>5.78</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>15</v>
@@ -2724,7 +2724,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>23</v>
@@ -2742,7 +2742,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5.78</v>
+        <v>5.66</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>15</v>
@@ -2756,7 +2756,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>25</v>
@@ -2774,7 +2774,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5.66</v>
+        <v>5.11</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>15</v>
@@ -2785,7 +2785,7 @@
         <v>2019</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
@@ -2806,7 +2806,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5.53</v>
+        <v>3.53</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>15</v>
@@ -2820,7 +2820,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>29</v>
@@ -2838,7 +2838,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5.11</v>
+        <v>3.05</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>15</v>
@@ -2849,7 +2849,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
@@ -2870,7 +2870,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3.53</v>
+        <v>3.03</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>15</v>
@@ -2884,7 +2884,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>33</v>
@@ -2902,7 +2902,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>15</v>
@@ -2913,7 +2913,7 @@
         <v>2019</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
@@ -2934,7 +2934,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3.03</v>
+        <v>2.51</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>15</v>
@@ -2945,7 +2945,7 @@
         <v>2019</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>10</v>
@@ -2966,7 +2966,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>15</v>
@@ -2980,7 +2980,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>39</v>
@@ -2998,7 +2998,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>15</v>
@@ -3012,7 +3012,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>41</v>
@@ -3030,7 +3030,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2.44</v>
+        <v>1.74</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>15</v>
@@ -3044,7 +3044,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>43</v>
@@ -3062,7 +3062,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>15</v>
@@ -3073,28 +3073,28 @@
         <v>2019</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.74</v>
+        <v>6.83</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>15</v>
@@ -3105,28 +3105,28 @@
         <v>2019</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>15</v>
@@ -3137,28 +3137,28 @@
         <v>2019</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6.83</v>
+        <v>5.95</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>15</v>
@@ -3169,28 +3169,28 @@
         <v>2019</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6.51</v>
+        <v>5.63</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>15</v>
@@ -3201,10 +3201,10 @@
         <v>2019</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>58</v>
@@ -3213,16 +3213,16 @@
         <v>59</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5.95</v>
+        <v>5.57</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>15</v>
@@ -3236,7 +3236,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>60</v>
@@ -3245,16 +3245,16 @@
         <v>61</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5.63</v>
+        <v>5.51</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>15</v>
@@ -3265,10 +3265,10 @@
         <v>2019</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>62</v>
@@ -3277,16 +3277,16 @@
         <v>63</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>5.57</v>
+        <v>5.45</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>15</v>
@@ -3297,28 +3297,28 @@
         <v>2019</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5.51</v>
+        <v>5.34</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>15</v>
@@ -3329,28 +3329,28 @@
         <v>2019</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>15</v>
@@ -3361,28 +3361,28 @@
         <v>2019</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>5.34</v>
+        <v>5.08</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>15</v>
@@ -3393,10 +3393,10 @@
         <v>2019</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>72</v>
@@ -3405,16 +3405,16 @@
         <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5.3</v>
+        <v>5.05</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>15</v>
@@ -3425,10 +3425,10 @@
         <v>2019</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>74</v>
@@ -3437,16 +3437,16 @@
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5.08</v>
+        <v>5.05</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>15</v>
@@ -3460,7 +3460,7 @@
         <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3469,16 +3469,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5.05</v>
+        <v>5.02</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>15</v>
@@ -3489,10 +3489,10 @@
         <v>2019</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3501,16 +3501,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5.05</v>
+        <v>4.93</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>15</v>
@@ -3521,10 +3521,10 @@
         <v>2019</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3533,16 +3533,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>5.02</v>
+        <v>4.85</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>15</v>
@@ -3556,7 +3556,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3565,16 +3565,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4.93</v>
+        <v>4.84</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>15</v>
@@ -3588,7 +3588,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3597,16 +3597,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>15</v>
@@ -3617,10 +3617,10 @@
         <v>2019</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3629,16 +3629,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>15</v>
@@ -3652,7 +3652,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3661,16 +3661,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>4.81</v>
+        <v>4.79</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>15</v>
@@ -3681,10 +3681,10 @@
         <v>2019</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3693,16 +3693,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>15</v>
@@ -3716,7 +3716,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3725,16 +3725,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>15</v>
@@ -3745,10 +3745,10 @@
         <v>2019</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3757,16 +3757,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>15</v>
@@ -3780,7 +3780,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3789,16 +3789,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>15</v>
@@ -3809,10 +3809,10 @@
         <v>2019</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3821,16 +3821,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>15</v>
@@ -3841,10 +3841,10 @@
         <v>2019</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3853,16 +3853,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>15</v>
@@ -3873,10 +3873,10 @@
         <v>2019</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3885,16 +3885,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>15</v>
@@ -3905,10 +3905,10 @@
         <v>2019</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
@@ -3917,16 +3917,16 @@
         <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>4.69</v>
+        <v>4.64</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>15</v>
@@ -3937,10 +3937,10 @@
         <v>2019</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>106</v>
@@ -3949,16 +3949,16 @@
         <v>107</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>15</v>
@@ -3969,10 +3969,10 @@
         <v>2019</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
@@ -3981,16 +3981,16 @@
         <v>109</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>4.64</v>
+        <v>4.55</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>15</v>
@@ -4004,7 +4004,7 @@
         <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>110</v>
@@ -4013,16 +4013,16 @@
         <v>111</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>15</v>
@@ -4033,10 +4033,10 @@
         <v>2019</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>112</v>
@@ -4045,16 +4045,16 @@
         <v>113</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>15</v>
@@ -4068,7 +4068,7 @@
         <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>114</v>
@@ -4077,16 +4077,16 @@
         <v>115</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>4.53</v>
+        <v>4.51</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -4097,10 +4097,10 @@
         <v>2019</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>116</v>
@@ -4109,16 +4109,16 @@
         <v>117</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>15</v>
@@ -4129,10 +4129,10 @@
         <v>2019</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>118</v>
@@ -4141,16 +4141,16 @@
         <v>119</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>4.51</v>
+        <v>4.46</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>15</v>
@@ -4161,10 +4161,10 @@
         <v>2019</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>120</v>
@@ -4173,10 +4173,10 @@
         <v>121</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -4193,10 +4193,10 @@
         <v>2019</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>122</v>
@@ -4205,16 +4205,16 @@
         <v>123</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>15</v>
@@ -4225,10 +4225,10 @@
         <v>2019</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>124</v>
@@ -4237,16 +4237,16 @@
         <v>125</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>15</v>
@@ -4260,7 +4260,7 @@
         <v>6</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>126</v>
@@ -4269,16 +4269,16 @@
         <v>127</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>15</v>
@@ -4289,10 +4289,10 @@
         <v>2019</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>128</v>
@@ -4301,16 +4301,16 @@
         <v>129</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>15</v>
@@ -4321,10 +4321,10 @@
         <v>2019</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>130</v>
@@ -4333,16 +4333,16 @@
         <v>131</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>15</v>
@@ -4353,10 +4353,10 @@
         <v>2019</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>132</v>
@@ -4365,16 +4365,16 @@
         <v>133</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>15</v>
@@ -4385,10 +4385,10 @@
         <v>2019</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>134</v>
@@ -4397,16 +4397,16 @@
         <v>135</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>15</v>
@@ -4417,10 +4417,10 @@
         <v>2019</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>136</v>
@@ -4429,16 +4429,16 @@
         <v>137</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>15</v>
@@ -4449,10 +4449,10 @@
         <v>2019</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>138</v>
@@ -4461,16 +4461,16 @@
         <v>139</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>15</v>
@@ -4484,7 +4484,7 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>140</v>
@@ -4493,16 +4493,16 @@
         <v>141</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4.35</v>
+        <v>4.27</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>15</v>
@@ -4516,7 +4516,7 @@
         <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
@@ -4525,16 +4525,16 @@
         <v>143</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>4.34</v>
+        <v>4.27</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>15</v>
@@ -4545,10 +4545,10 @@
         <v>2019</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>144</v>
@@ -4557,16 +4557,16 @@
         <v>145</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>15</v>
@@ -4577,10 +4577,10 @@
         <v>2019</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
@@ -4589,16 +4589,16 @@
         <v>147</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>15</v>
@@ -4609,10 +4609,10 @@
         <v>2019</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>148</v>
@@ -4621,16 +4621,16 @@
         <v>149</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>15</v>
@@ -4641,10 +4641,10 @@
         <v>2019</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>150</v>
@@ -4653,16 +4653,16 @@
         <v>151</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>4.21</v>
+        <v>4.12</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>15</v>
@@ -4673,10 +4673,10 @@
         <v>2019</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>152</v>
@@ -4685,16 +4685,16 @@
         <v>153</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>15</v>
@@ -4708,7 +4708,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>154</v>
@@ -4717,16 +4717,16 @@
         <v>155</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>15</v>
@@ -4737,10 +4737,10 @@
         <v>2019</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4749,16 +4749,16 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>15</v>
@@ -4772,7 +4772,7 @@
         <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4781,16 +4781,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>15</v>
@@ -4804,7 +4804,7 @@
         <v>6</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4813,16 +4813,16 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>15</v>
@@ -4833,10 +4833,10 @@
         <v>2019</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4845,16 +4845,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>15</v>
@@ -4865,10 +4865,10 @@
         <v>2019</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4877,16 +4877,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>15</v>
@@ -4897,10 +4897,10 @@
         <v>2019</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4909,16 +4909,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>15</v>
@@ -4929,10 +4929,10 @@
         <v>2019</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4941,16 +4941,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4.06</v>
+        <v>4.01</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>15</v>
@@ -4961,10 +4961,10 @@
         <v>2019</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4973,16 +4973,16 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>15</v>
@@ -4993,10 +4993,10 @@
         <v>2019</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -5005,16 +5005,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>15</v>
@@ -5025,10 +5025,10 @@
         <v>2019</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -5037,16 +5037,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>15</v>
@@ -5057,10 +5057,10 @@
         <v>2019</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -5069,16 +5069,16 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>15</v>
@@ -5089,10 +5089,10 @@
         <v>2019</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -5101,16 +5101,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>15</v>
@@ -5121,10 +5121,10 @@
         <v>2019</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -5133,16 +5133,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>15</v>
@@ -5153,10 +5153,10 @@
         <v>2019</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -5165,10 +5165,10 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -5185,10 +5185,10 @@
         <v>2019</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5197,16 +5197,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>15</v>
@@ -5217,10 +5217,10 @@
         <v>2019</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5229,16 +5229,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>15</v>
@@ -5249,10 +5249,10 @@
         <v>2019</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5261,16 +5261,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>15</v>
@@ -5281,10 +5281,10 @@
         <v>2019</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5293,16 +5293,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>15</v>
@@ -5313,10 +5313,10 @@
         <v>2019</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5325,16 +5325,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>15</v>
@@ -5345,10 +5345,10 @@
         <v>2019</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5357,16 +5357,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>15</v>
@@ -5377,10 +5377,10 @@
         <v>2019</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5389,16 +5389,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>15</v>
@@ -5409,10 +5409,10 @@
         <v>2019</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5421,16 +5421,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>15</v>
@@ -5441,10 +5441,10 @@
         <v>2019</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5453,16 +5453,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>15</v>
@@ -5473,10 +5473,10 @@
         <v>2019</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5485,16 +5485,16 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>15</v>
@@ -5508,7 +5508,7 @@
         <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5517,16 +5517,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>15</v>
@@ -5537,10 +5537,10 @@
         <v>2019</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5549,16 +5549,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>15</v>
@@ -5569,10 +5569,10 @@
         <v>2019</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5581,16 +5581,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>15</v>
@@ -5601,10 +5601,10 @@
         <v>2019</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5613,16 +5613,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>15</v>
@@ -5633,10 +5633,10 @@
         <v>2019</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5645,16 +5645,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>15</v>
@@ -5665,10 +5665,10 @@
         <v>2019</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5677,16 +5677,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>15</v>
@@ -5697,10 +5697,10 @@
         <v>2019</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5709,16 +5709,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>15</v>
@@ -5732,7 +5732,7 @@
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5741,16 +5741,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>15</v>
@@ -5761,10 +5761,10 @@
         <v>2019</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5773,16 +5773,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>15</v>
@@ -5796,7 +5796,7 @@
         <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5805,16 +5805,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>15</v>
@@ -5825,10 +5825,10 @@
         <v>2019</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5837,16 +5837,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>15</v>
@@ -5857,10 +5857,10 @@
         <v>2019</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5869,16 +5869,16 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>15</v>
@@ -5892,7 +5892,7 @@
         <v>7</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5901,16 +5901,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>15</v>
@@ -5921,10 +5921,10 @@
         <v>2019</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5933,16 +5933,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>15</v>
@@ -5953,10 +5953,10 @@
         <v>2019</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5965,16 +5965,16 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>15</v>
@@ -5985,10 +5985,10 @@
         <v>2019</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5997,16 +5997,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>15</v>
@@ -6017,10 +6017,10 @@
         <v>2019</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -6029,16 +6029,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>15</v>
@@ -6049,10 +6049,10 @@
         <v>2019</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -6061,16 +6061,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>15</v>
@@ -6081,10 +6081,10 @@
         <v>2019</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6093,16 +6093,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>15</v>
@@ -6113,10 +6113,10 @@
         <v>2019</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6125,16 +6125,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>15</v>
@@ -6145,10 +6145,10 @@
         <v>2019</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6157,16 +6157,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>15</v>
@@ -6177,10 +6177,10 @@
         <v>2019</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6189,10 +6189,10 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6212,7 +6212,7 @@
         <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6221,16 +6221,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>15</v>
@@ -6241,10 +6241,10 @@
         <v>2019</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6253,16 +6253,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>15</v>
@@ -6273,10 +6273,10 @@
         <v>2019</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6285,16 +6285,16 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>15</v>
@@ -6305,10 +6305,10 @@
         <v>2019</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6317,16 +6317,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>15</v>
@@ -6337,10 +6337,10 @@
         <v>2019</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6349,16 +6349,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>15</v>
@@ -6369,10 +6369,10 @@
         <v>2019</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6381,16 +6381,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>15</v>
@@ -6404,7 +6404,7 @@
         <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6413,16 +6413,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>15</v>
@@ -6433,10 +6433,10 @@
         <v>2019</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6445,16 +6445,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>15</v>
@@ -6465,10 +6465,10 @@
         <v>2019</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6477,16 +6477,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>15</v>
@@ -6497,10 +6497,10 @@
         <v>2019</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6509,16 +6509,16 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>15</v>
@@ -6529,10 +6529,10 @@
         <v>2019</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6541,16 +6541,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>3.46</v>
+        <v>3.39</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>15</v>
@@ -6561,10 +6561,10 @@
         <v>2019</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6573,16 +6573,16 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>15</v>
@@ -6593,10 +6593,10 @@
         <v>2019</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6605,16 +6605,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>15</v>
@@ -6625,10 +6625,10 @@
         <v>2019</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6637,10 +6637,10 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6657,10 +6657,10 @@
         <v>2019</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6669,16 +6669,16 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>15</v>
@@ -6689,10 +6689,10 @@
         <v>2019</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6701,16 +6701,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>15</v>
@@ -6724,7 +6724,7 @@
         <v>7</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6733,16 +6733,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>3.36</v>
+        <v>3.29</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>15</v>
@@ -6753,10 +6753,10 @@
         <v>2019</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6765,16 +6765,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>15</v>
@@ -6785,10 +6785,10 @@
         <v>2019</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6797,16 +6797,16 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>15</v>
@@ -6820,7 +6820,7 @@
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6829,16 +6829,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>15</v>
@@ -6852,7 +6852,7 @@
         <v>5</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6861,16 +6861,16 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>15</v>
@@ -6881,10 +6881,10 @@
         <v>2019</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6893,16 +6893,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>15</v>
@@ -6913,10 +6913,10 @@
         <v>2019</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6925,16 +6925,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>15</v>
@@ -6948,7 +6948,7 @@
         <v>16</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6957,16 +6957,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>15</v>
@@ -6977,10 +6977,10 @@
         <v>2019</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6989,16 +6989,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>15</v>
@@ -7009,10 +7009,10 @@
         <v>2019</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -7021,16 +7021,16 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>15</v>
@@ -7041,10 +7041,10 @@
         <v>2019</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -7053,16 +7053,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>15</v>
@@ -7073,10 +7073,10 @@
         <v>2019</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7085,16 +7085,16 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>15</v>
@@ -7105,10 +7105,10 @@
         <v>2019</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7117,16 +7117,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>15</v>
@@ -7137,10 +7137,10 @@
         <v>2019</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7149,10 +7149,10 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7169,10 +7169,10 @@
         <v>2019</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7181,16 +7181,16 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>15</v>
@@ -7204,7 +7204,7 @@
         <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7213,10 +7213,10 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7233,10 +7233,10 @@
         <v>2019</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7245,16 +7245,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>15</v>
@@ -7265,10 +7265,10 @@
         <v>2019</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7277,10 +7277,10 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7297,10 +7297,10 @@
         <v>2019</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7309,16 +7309,16 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>15</v>
@@ -7329,10 +7329,10 @@
         <v>2019</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7341,16 +7341,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>15</v>
@@ -7361,10 +7361,10 @@
         <v>2019</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7373,16 +7373,16 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>15</v>
@@ -7393,10 +7393,10 @@
         <v>2019</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7405,16 +7405,16 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>15</v>
@@ -7425,10 +7425,10 @@
         <v>2019</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7437,16 +7437,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>15</v>
@@ -7457,10 +7457,10 @@
         <v>2019</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7469,16 +7469,16 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>15</v>
@@ -7489,10 +7489,10 @@
         <v>2019</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7501,16 +7501,16 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>15</v>
@@ -7521,10 +7521,10 @@
         <v>2019</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7533,10 +7533,10 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7553,10 +7553,10 @@
         <v>2019</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7565,10 +7565,10 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7585,10 +7585,10 @@
         <v>2019</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7597,16 +7597,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>15</v>
@@ -7620,7 +7620,7 @@
         <v>7</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7629,16 +7629,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>15</v>
@@ -7649,10 +7649,10 @@
         <v>2019</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7661,16 +7661,16 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>15</v>
@@ -7681,10 +7681,10 @@
         <v>2019</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7693,16 +7693,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>15</v>
@@ -7713,28 +7713,28 @@
         <v>2019</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>343</v>
+        <v>45</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>15</v>
@@ -7745,28 +7745,28 @@
         <v>2019</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D163" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E163" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="F163" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>15</v>
@@ -7780,7 +7780,7 @@
         <v>6</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>345</v>
@@ -7789,16 +7789,16 @@
         <v>346</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>15</v>
@@ -7812,7 +7812,7 @@
         <v>6</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>347</v>
@@ -7821,16 +7821,16 @@
         <v>348</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>15</v>
@@ -7841,10 +7841,10 @@
         <v>2019</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>349</v>
@@ -7853,16 +7853,16 @@
         <v>350</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>15</v>
@@ -7873,10 +7873,10 @@
         <v>2019</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>351</v>
@@ -7885,16 +7885,16 @@
         <v>352</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>15</v>
@@ -7905,10 +7905,10 @@
         <v>2019</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>353</v>
@@ -7917,10 +7917,10 @@
         <v>354</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7937,10 +7937,10 @@
         <v>2019</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>355</v>
@@ -7949,16 +7949,16 @@
         <v>356</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>15</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>357</v>
@@ -7981,16 +7981,16 @@
         <v>358</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>15</v>
@@ -8001,10 +8001,10 @@
         <v>2019</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>359</v>
@@ -8013,16 +8013,16 @@
         <v>360</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>15</v>
@@ -8033,10 +8033,10 @@
         <v>2019</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>361</v>
@@ -8045,16 +8045,16 @@
         <v>362</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>15</v>
@@ -8065,10 +8065,10 @@
         <v>2019</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>363</v>
@@ -8077,16 +8077,16 @@
         <v>364</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>15</v>
@@ -8097,10 +8097,10 @@
         <v>2019</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>365</v>
@@ -8109,16 +8109,16 @@
         <v>366</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>15</v>
@@ -8129,10 +8129,10 @@
         <v>2019</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>367</v>
@@ -8141,16 +8141,16 @@
         <v>368</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>15</v>
@@ -8161,10 +8161,10 @@
         <v>2019</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>369</v>
@@ -8173,16 +8173,16 @@
         <v>370</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>15</v>
@@ -8196,7 +8196,7 @@
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>371</v>
@@ -8205,16 +8205,16 @@
         <v>372</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>15</v>
@@ -8228,7 +8228,7 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>373</v>
@@ -8237,16 +8237,16 @@
         <v>374</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>15</v>
@@ -8257,10 +8257,10 @@
         <v>2019</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>375</v>
@@ -8269,16 +8269,16 @@
         <v>376</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>15</v>
@@ -8289,10 +8289,10 @@
         <v>2019</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8301,16 +8301,16 @@
         <v>378</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>15</v>
@@ -8321,10 +8321,10 @@
         <v>2019</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>379</v>
@@ -8333,16 +8333,16 @@
         <v>380</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>15</v>
@@ -8353,10 +8353,10 @@
         <v>2019</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>381</v>
@@ -8365,16 +8365,16 @@
         <v>382</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>15</v>
@@ -8388,7 +8388,7 @@
         <v>6</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>383</v>
@@ -8397,16 +8397,16 @@
         <v>384</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>15</v>
@@ -8417,10 +8417,10 @@
         <v>2019</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>385</v>
@@ -8429,16 +8429,16 @@
         <v>386</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>15</v>
@@ -8449,10 +8449,10 @@
         <v>2019</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>387</v>
@@ -8461,16 +8461,16 @@
         <v>388</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>15</v>
@@ -8481,10 +8481,10 @@
         <v>2019</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>389</v>
@@ -8493,16 +8493,16 @@
         <v>390</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>15</v>
@@ -8513,10 +8513,10 @@
         <v>2019</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>391</v>
@@ -8525,16 +8525,16 @@
         <v>392</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>15</v>
@@ -8548,7 +8548,7 @@
         <v>13</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>393</v>
@@ -8557,16 +8557,16 @@
         <v>394</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>1.22</v>
+        <v>0.85</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>15</v>
@@ -8577,28 +8577,28 @@
         <v>2019</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>57</v>
+        <v>395</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>52</v>
+        <v>398</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>53</v>
+        <v>399</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>0.85</v>
+        <v>6.25</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>15</v>
@@ -8609,28 +8609,28 @@
         <v>2019</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D190" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F190" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="E190" s="2" t="s">
+      <c r="G190" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="F190" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="G190" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>15</v>
@@ -8641,28 +8641,28 @@
         <v>2019</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>15</v>
@@ -8673,10 +8673,10 @@
         <v>2019</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>406</v>
@@ -8685,16 +8685,16 @@
         <v>407</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>15</v>
@@ -8705,28 +8705,28 @@
         <v>2019</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>15</v>
@@ -8740,7 +8740,7 @@
         <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>411</v>
@@ -8749,16 +8749,16 @@
         <v>412</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>15</v>
@@ -8769,10 +8769,10 @@
         <v>2019</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>413</v>
@@ -8781,16 +8781,16 @@
         <v>414</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>5.22</v>
+        <v>5.16</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>15</v>
@@ -8801,28 +8801,28 @@
         <v>2019</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>5.16</v>
+        <v>4.99</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>15</v>
@@ -8833,10 +8833,10 @@
         <v>2019</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>418</v>
@@ -8845,16 +8845,16 @@
         <v>419</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>4.99</v>
+        <v>4.97</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>15</v>
@@ -8865,10 +8865,10 @@
         <v>2019</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>420</v>
@@ -8877,16 +8877,16 @@
         <v>421</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>15</v>
@@ -8897,10 +8897,10 @@
         <v>2019</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>422</v>
@@ -8909,16 +8909,16 @@
         <v>423</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>4.96</v>
+        <v>4.77</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>15</v>
@@ -8932,7 +8932,7 @@
         <v>3</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>424</v>
@@ -8941,16 +8941,16 @@
         <v>425</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>4.77</v>
+        <v>4.67</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>15</v>
@@ -8961,10 +8961,10 @@
         <v>2019</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>426</v>
@@ -8973,16 +8973,16 @@
         <v>427</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>4.67</v>
+        <v>4.51</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>15</v>
@@ -8993,10 +8993,10 @@
         <v>2019</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>428</v>
@@ -9005,16 +9005,16 @@
         <v>429</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>4.51</v>
+        <v>4.13</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>15</v>
@@ -9028,7 +9028,7 @@
         <v>1</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>430</v>
@@ -9037,16 +9037,16 @@
         <v>431</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>15</v>
@@ -9057,10 +9057,10 @@
         <v>2019</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>432</v>
@@ -9069,16 +9069,16 @@
         <v>433</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>15</v>
@@ -9092,7 +9092,7 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>434</v>
@@ -9101,10 +9101,10 @@
         <v>435</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9124,19 +9124,19 @@
         <v>2</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>436</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9156,19 +9156,19 @@
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>437</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9188,7 +9188,7 @@
         <v>3</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>438</v>
@@ -9197,10 +9197,10 @@
         <v>439</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9220,7 +9220,7 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>440</v>
@@ -9229,10 +9229,10 @@
         <v>441</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9252,7 +9252,7 @@
         <v>3</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>442</v>
@@ -9261,10 +9261,10 @@
         <v>443</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9284,7 +9284,7 @@
         <v>2</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>444</v>
@@ -9293,10 +9293,10 @@
         <v>445</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9316,7 +9316,7 @@
         <v>1</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>446</v>
@@ -9325,10 +9325,10 @@
         <v>447</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9348,7 +9348,7 @@
         <v>2</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>448</v>
@@ -9357,10 +9357,10 @@
         <v>449</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9380,7 +9380,7 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>450</v>
@@ -9389,10 +9389,10 @@
         <v>451</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9412,7 +9412,7 @@
         <v>15</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>452</v>
@@ -9421,10 +9421,10 @@
         <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9444,7 +9444,7 @@
         <v>3</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>454</v>
@@ -9453,10 +9453,10 @@
         <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9476,7 +9476,7 @@
         <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>456</v>
@@ -9485,10 +9485,10 @@
         <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9508,7 +9508,7 @@
         <v>2</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>458</v>
@@ -9517,10 +9517,10 @@
         <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9540,7 +9540,7 @@
         <v>15</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>460</v>
@@ -9549,10 +9549,10 @@
         <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9572,7 +9572,7 @@
         <v>3</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>462</v>
@@ -9581,10 +9581,10 @@
         <v>463</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9604,7 +9604,7 @@
         <v>4</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>464</v>
@@ -9613,10 +9613,10 @@
         <v>465</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9636,7 +9636,7 @@
         <v>4</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>466</v>
@@ -9645,10 +9645,10 @@
         <v>467</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9668,7 +9668,7 @@
         <v>4</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>468</v>
@@ -9677,10 +9677,10 @@
         <v>469</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9700,7 +9700,7 @@
         <v>3</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>470</v>
@@ -9709,10 +9709,10 @@
         <v>471</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9732,7 +9732,7 @@
         <v>3</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>472</v>
@@ -9741,10 +9741,10 @@
         <v>473</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9764,7 +9764,7 @@
         <v>4</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>474</v>
@@ -9773,10 +9773,10 @@
         <v>475</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9796,7 +9796,7 @@
         <v>2</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>476</v>
@@ -9805,10 +9805,10 @@
         <v>477</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9828,7 +9828,7 @@
         <v>4</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>478</v>
@@ -9837,10 +9837,10 @@
         <v>479</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9860,7 +9860,7 @@
         <v>1</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>480</v>
@@ -9869,10 +9869,10 @@
         <v>481</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9892,7 +9892,7 @@
         <v>4</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>482</v>
@@ -9901,10 +9901,10 @@
         <v>483</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
@@ -367,18 +367,18 @@
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
+    <t xml:space="preserve">5706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
     <t xml:space="preserve">5801</t>
   </si>
   <si>
     <t xml:space="preserve">Quilpué</t>
   </si>
   <si>
-    <t xml:space="preserve">5706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa María</t>
-  </si>
-  <si>
     <t xml:space="preserve">7405</t>
   </si>
   <si>
@@ -745,18 +745,18 @@
     <t xml:space="preserve">Rinconada</t>
   </si>
   <si>
+    <t xml:space="preserve">13126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
     <t xml:space="preserve">13501</t>
   </si>
   <si>
     <t xml:space="preserve">Melipilla</t>
   </si>
   <si>
-    <t xml:space="preserve">13126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta Normal</t>
-  </si>
-  <si>
     <t xml:space="preserve">6308</t>
   </si>
   <si>
@@ -787,18 +787,18 @@
     <t xml:space="preserve">San Nicolás</t>
   </si>
   <si>
+    <t xml:space="preserve">13107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
     <t xml:space="preserve">13503</t>
   </si>
   <si>
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
-    <t xml:space="preserve">13107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
     <t xml:space="preserve">13303</t>
   </si>
   <si>
@@ -1594,18 +1594,18 @@
     <t xml:space="preserve">Cochamó</t>
   </si>
   <si>
+    <t xml:space="preserve">8207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirúa</t>
+  </si>
+  <si>
     <t xml:space="preserve">8310</t>
   </si>
   <si>
     <t xml:space="preserve">San Rosendo</t>
   </si>
   <si>
-    <t xml:space="preserve">8207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirúa</t>
-  </si>
-  <si>
     <t xml:space="preserve">10307</t>
   </si>
   <si>
@@ -1699,18 +1699,18 @@
     <t xml:space="preserve">Frutillar</t>
   </si>
   <si>
+    <t xml:space="preserve">10101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Montt</t>
+  </si>
+  <si>
     <t xml:space="preserve">10401</t>
   </si>
   <si>
     <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
-    <t xml:space="preserve">10101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Montt</t>
-  </si>
-  <si>
     <t xml:space="preserve">14101</t>
   </si>
   <si>
@@ -2059,18 +2059,18 @@
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
+    <t xml:space="preserve">9110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipeuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">9203</t>
   </si>
   <si>
     <t xml:space="preserve">Curacautín</t>
   </si>
   <si>
-    <t xml:space="preserve">9110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipeuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">8313</t>
   </si>
   <si>
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:21</t>
+    <t xml:space="preserve">2026-09-18 11:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
